--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-cs-note-type.xlsx
+++ b/main/ig/CodeSystem-fr-cs-note-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
